--- a/diseases/d205/2010-2014.xlsx
+++ b/diseases/d205/2010-2014.xlsx
@@ -17186,7 +17186,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23642,7 +23642,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30542,7 +30542,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30944,7 +30944,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31748,7 +31748,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32150,7 +32150,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34048,7 +34048,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34450,7 +34450,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35544,7 +35544,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36750,7 +36750,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37844,7 +37844,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38648,7 +38648,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39452,7 +39452,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40546,7 +40546,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40948,7 +40948,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41350,7 +41350,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41752,7 +41752,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42846,7 +42846,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44052,7 +44052,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44998,7 +44998,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45950,7 +45950,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46352,7 +46352,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46754,7 +46754,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47848,7 +47848,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48250,7 +48250,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50148,7 +50148,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50550,7 +50550,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50952,7 +50952,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51354,7 +51354,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52300,7 +52300,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52850,7 +52850,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53252,7 +53252,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53654,7 +53654,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54056,7 +54056,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55150,7 +55150,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55552,7 +55552,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55954,7 +55954,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56356,7 +56356,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -57450,7 +57450,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -57852,7 +57852,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -58254,7 +58254,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58656,7 +58656,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -59750,7 +59750,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -60152,7 +60152,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60554,7 +60554,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60956,7 +60956,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61358,7 +61358,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -62854,7 +62854,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -63256,7 +63256,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -63658,7 +63658,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64752,7 +64752,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -65154,7 +65154,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65556,7 +65556,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65958,7 +65958,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -66904,7 +66904,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -67454,7 +67454,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67856,7 +67856,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68258,7 +68258,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -68660,7 +68660,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -69754,7 +69754,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -70156,7 +70156,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70558,7 +70558,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70960,7 +70960,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -72054,7 +72054,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72456,7 +72456,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72858,7 +72858,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -73260,7 +73260,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73662,7 +73662,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -74756,7 +74756,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -75158,7 +75158,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -75560,7 +75560,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75962,7 +75962,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -77056,7 +77056,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77458,7 +77458,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77860,7 +77860,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -78262,7 +78262,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -79356,7 +79356,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79758,7 +79758,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -80160,7 +80160,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -80562,7 +80562,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80964,7 +80964,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -82058,7 +82058,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -82460,7 +82460,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -82862,7 +82862,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -83264,7 +83264,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">

--- a/diseases/d205/2010-2014.xlsx
+++ b/diseases/d205/2010-2014.xlsx
@@ -17186,7 +17186,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23642,7 +23642,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30542,7 +30542,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30944,7 +30944,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31748,7 +31748,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32150,7 +32150,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34048,7 +34048,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34450,7 +34450,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35544,7 +35544,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36750,7 +36750,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37844,7 +37844,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38648,7 +38648,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39452,7 +39452,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40546,7 +40546,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40948,7 +40948,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41350,7 +41350,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41752,7 +41752,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42846,7 +42846,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44052,7 +44052,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44998,7 +44998,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45950,7 +45950,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46352,7 +46352,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46754,7 +46754,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47848,7 +47848,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48250,7 +48250,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50148,7 +50148,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50550,7 +50550,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50952,7 +50952,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51354,7 +51354,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52300,7 +52300,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52850,7 +52850,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53252,7 +53252,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53654,7 +53654,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54056,7 +54056,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55150,7 +55150,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55552,7 +55552,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55954,7 +55954,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56356,7 +56356,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -57450,7 +57450,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -57852,7 +57852,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -58254,7 +58254,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58656,7 +58656,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -59750,7 +59750,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -60152,7 +60152,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60554,7 +60554,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60956,7 +60956,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61358,7 +61358,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -62854,7 +62854,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -63256,7 +63256,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -63658,7 +63658,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64752,7 +64752,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -65154,7 +65154,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65556,7 +65556,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65958,7 +65958,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -66904,7 +66904,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -67454,7 +67454,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67856,7 +67856,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68258,7 +68258,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -68660,7 +68660,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -69754,7 +69754,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -70156,7 +70156,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70558,7 +70558,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70960,7 +70960,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -72054,7 +72054,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72456,7 +72456,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72858,7 +72858,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -73260,7 +73260,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73662,7 +73662,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -74756,7 +74756,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -75158,7 +75158,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -75560,7 +75560,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75962,7 +75962,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -77056,7 +77056,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77458,7 +77458,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77860,7 +77860,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -78262,7 +78262,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -79356,7 +79356,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79758,7 +79758,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -80160,7 +80160,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -80562,7 +80562,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80964,7 +80964,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -82058,7 +82058,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -82460,7 +82460,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -82862,7 +82862,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -83264,7 +83264,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">

--- a/diseases/d205/2010-2014.xlsx
+++ b/diseases/d205/2010-2014.xlsx
@@ -17021,7 +17021,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27987,7 +27987,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30269,7 +30269,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31067,7 +31067,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33349,7 +33349,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34147,7 +34147,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35631,7 +35631,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36030,7 +36030,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36429,7 +36429,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -37913,7 +37913,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38711,7 +38711,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40195,7 +40195,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40594,7 +40594,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -40993,7 +40993,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41392,7 +41392,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -42876,7 +42876,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44614,7 +44614,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45557,7 +45557,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -45956,7 +45956,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47440,7 +47440,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -47839,7 +47839,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48238,7 +48238,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48637,7 +48637,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49722,7 +49722,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50121,7 +50121,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50520,7 +50520,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -50919,7 +50919,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51859,7 +51859,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52403,7 +52403,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -52802,7 +52802,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53201,7 +53201,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -53600,7 +53600,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54685,7 +54685,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55084,7 +55084,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55483,7 +55483,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -55882,7 +55882,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -56967,7 +56967,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -57366,7 +57366,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -57765,7 +57765,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58164,7 +58164,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -59249,7 +59249,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59648,7 +59648,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60047,7 +60047,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60446,7 +60446,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60845,7 +60845,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61930,7 +61930,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -62329,7 +62329,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62728,7 +62728,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -63127,7 +63127,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64212,7 +64212,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64611,7 +64611,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65010,7 +65010,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65409,7 +65409,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -66349,7 +66349,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -66893,7 +66893,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67292,7 +67292,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -67691,7 +67691,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -68090,7 +68090,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -69175,7 +69175,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -69574,7 +69574,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -69973,7 +69973,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70372,7 +70372,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71457,7 +71457,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -71856,7 +71856,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72255,7 +72255,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -72654,7 +72654,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73053,7 +73053,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -74138,7 +74138,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74537,7 +74537,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -74936,7 +74936,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75335,7 +75335,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76420,7 +76420,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -76819,7 +76819,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77218,7 +77218,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77617,7 +77617,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -78702,7 +78702,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79101,7 +79101,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -79500,7 +79500,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -79899,7 +79899,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80298,7 +80298,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81383,7 +81383,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -81782,7 +81782,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -82181,7 +82181,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -82580,7 +82580,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
